--- a/resources/outputs_schema_data_analytics_fsl_template.xlsx
+++ b/resources/outputs_schema_data_analytics_fsl_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B27CD6-E790-4CF3-9872-5C9BE49A6F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A8D4994-93DE-4F0F-99BE-E8FAA214C575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
